--- a/2026/FLORES DE ESTRADA/ENERO/EDESUR Enero.xlsx
+++ b/2026/FLORES DE ESTRADA/ENERO/EDESUR Enero.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\FLORES DE ESTRADA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469B7B01-186B-47AB-923A-1C21A39499B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFBEEE5-1644-4173-BF5A-922F4F03A434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -627,6 +627,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -642,7 +643,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,21 +967,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="61"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="62"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1860,7 +1860,7 @@
       <c r="C21" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="66" t="s">
+      <c r="D21" s="59" t="s">
         <v>64</v>
       </c>
       <c r="E21" s="39">
@@ -2545,7 +2545,7 @@
       <c r="C33" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="66" t="s">
+      <c r="D33" s="59" t="s">
         <v>64</v>
       </c>
       <c r="E33" s="39">
@@ -2631,19 +2631,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="62" t="s">
+      <c r="C35" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="60"/>
-      <c r="K35" s="60"/>
-      <c r="L35" s="60"/>
-      <c r="M35" s="63"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="64"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -2667,80 +2667,80 @@
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="65"/>
-      <c r="L38" s="65"/>
-      <c r="M38" s="65"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="66"/>
+      <c r="L38" s="66"/>
+      <c r="M38" s="66"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="65"/>
-      <c r="C39" s="65"/>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="65"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="66"/>
+      <c r="J39" s="66"/>
+      <c r="K39" s="66"/>
+      <c r="L39" s="66"/>
+      <c r="M39" s="66"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="65"/>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="65"/>
-      <c r="L40" s="65"/>
-      <c r="M40" s="65"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="66"/>
+      <c r="L40" s="66"/>
+      <c r="M40" s="66"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="65"/>
-      <c r="C41" s="65"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="65"/>
-      <c r="L41" s="65"/>
-      <c r="M41" s="65"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
-      <c r="K42" s="65"/>
-      <c r="L42" s="65"/>
-      <c r="M42" s="65"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66"/>
+      <c r="J42" s="66"/>
+      <c r="K42" s="66"/>
+      <c r="L42" s="66"/>
+      <c r="M42" s="66"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6612,21 +6612,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="61"/>
+      <c r="A1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="62"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8218,19 +8218,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="62" t="s">
+      <c r="C35" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="60"/>
-      <c r="K35" s="60"/>
-      <c r="L35" s="60"/>
-      <c r="M35" s="63"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="64"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
